--- a/artfynd/A 57281-2022 artfynd.xlsx
+++ b/artfynd/A 57281-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57281-2022 artfynd.xlsx
+++ b/artfynd/A 57281-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104924107</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589201.9196125038</v>
+        <v>589202</v>
       </c>
       <c r="R2" t="n">
-        <v>6972983.249198199</v>
+        <v>6972983</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -760,19 +760,9 @@
           <t>2022-12-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-12-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -807,7 +797,7 @@
         <v>104924138</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -856,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589234.5257359014</v>
+        <v>589235</v>
       </c>
       <c r="R3" t="n">
-        <v>6972927.528436614</v>
+        <v>6972927</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,19 +879,9 @@
           <t>2022-12-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-12-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 57281-2022 artfynd.xlsx
+++ b/artfynd/A 57281-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104924107</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>104924138</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57281-2022 artfynd.xlsx
+++ b/artfynd/A 57281-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104924107</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>104924138</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57281-2022 artfynd.xlsx
+++ b/artfynd/A 57281-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104924107</v>
       </c>
       <c r="B2" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>104924138</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
